--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.658744626062126</v>
+        <v>1.244546001735096</v>
       </c>
       <c r="D2" t="n">
-        <v>10.91216145754678</v>
+        <v>1.773226236851352</v>
       </c>
       <c r="E2" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F2" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.02469414137231</v>
+        <v>1.629012797973001</v>
       </c>
       <c r="D3" t="n">
-        <v>9.786973934965156</v>
+        <v>1.590383264431838</v>
       </c>
       <c r="E3" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F3" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.65801570115543</v>
+        <v>5.794427551437757</v>
       </c>
       <c r="D4" t="n">
-        <v>33.22031926212121</v>
+        <v>5.398301880094697</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F4" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.94323210618491</v>
+        <v>6.490775217255048</v>
       </c>
       <c r="D5" t="n">
-        <v>39.55052271658555</v>
+        <v>6.426959941445153</v>
       </c>
       <c r="E5" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F5" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.41589789008621</v>
+        <v>5.10508340713901</v>
       </c>
       <c r="D6" t="n">
-        <v>30.81907915574106</v>
+        <v>5.008100362807923</v>
       </c>
       <c r="E6" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F6" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.464730456753</v>
+        <v>6.738018699222362</v>
       </c>
       <c r="D7" t="n">
-        <v>40.57734585999051</v>
+        <v>6.593818702248458</v>
       </c>
       <c r="E7" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F7" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.86326557943062</v>
+        <v>6.640280656657477</v>
       </c>
       <c r="D8" t="n">
-        <v>41.22151769018154</v>
+        <v>6.698496624654501</v>
       </c>
       <c r="E8" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F8" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.12685740270577</v>
+        <v>6.683114327939689</v>
       </c>
       <c r="D9" t="n">
-        <v>41.91689421560178</v>
+        <v>6.81149531003529</v>
       </c>
       <c r="E9" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F9" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.52500021359832</v>
+        <v>5.772812534709727</v>
       </c>
       <c r="D10" t="n">
-        <v>30.1888592591715</v>
+        <v>4.905689629615368</v>
       </c>
       <c r="E10" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F10" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.13639437855021</v>
+        <v>4.24716408651441</v>
       </c>
       <c r="D11" t="n">
-        <v>29.33685346847155</v>
+        <v>4.767238688626627</v>
       </c>
       <c r="E11" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F11" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.41044389590985</v>
+        <v>2.991697133085351</v>
       </c>
       <c r="D12" t="n">
-        <v>30.61744322164524</v>
+        <v>4.975334523517351</v>
       </c>
       <c r="E12" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F12" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>8.333333333333334</v>
+        <v>1.354166666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>12.18154139026714</v>
+        <v>1.97950047591841</v>
       </c>
       <c r="E13" t="n">
-        <v>12.9348348389565</v>
+        <v>2.101910661330431</v>
       </c>
       <c r="F13" t="n">
-        <v>11.42198846312919</v>
+        <v>1.856073125258494</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
